--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="192">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Entrée Rencontre</t>
+    <t>Rencontre</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -530,7 +530,13 @@
     <t>fr-lm-encounter.admission.admitSource</t>
   </si>
   <si>
-    <t>Source de l'admission (ex : référence d'un médecin, transfert).</t>
+    <t>Modalité d'entrée d'un patient en ES (urgence, programmée, etc...).</t>
+  </si>
+  <si>
+    <t>jdv-modalite-entree : Modalité d'entrée en établissement de santé</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-entree-cisis</t>
   </si>
   <si>
     <t>fr-lm-encounter.dischargeDiagnosis[x]</t>
@@ -546,13 +552,16 @@
     <t>fr-lm-encounter.dischargeDestination</t>
   </si>
   <si>
-    <t>Type et lieu de sortie</t>
+    <t>modalité de sortie du patient d'un ES (retour à domicile, EHPAD, HAD, etc...)</t>
   </si>
   <si>
     <t>fr-lm-encounter.dischargeDestination.type</t>
   </si>
   <si>
     <t>Type de sortie</t>
+  </si>
+  <si>
+    <t>JDV_ModaliteSortie_CISIS (1.2.250.1.213.1.1.5.74) ou autre JDV spécifique à un volet</t>
   </si>
   <si>
     <t>fr-lm-encounter.dischargeDestination.location[x]</t>
@@ -929,8 +938,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.16015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -3916,10 +3925,10 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -3954,10 +3963,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3980,13 +3989,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4037,7 +4046,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4054,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4083,10 +4092,10 @@
         <v>80</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4137,7 +4146,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4154,10 +4163,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4183,10 +4192,10 @@
         <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4216,7 +4225,7 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="Z33" t="s" s="2">
         <v>73</v>
@@ -4237,7 +4246,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4254,10 +4263,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4280,13 +4289,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4337,7 +4346,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4354,10 +4363,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4383,10 +4392,10 @@
         <v>80</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4437,7 +4446,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4454,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4483,10 +4492,10 @@
         <v>145</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4537,7 +4546,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4554,10 +4563,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4580,13 +4589,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4637,7 +4646,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -4654,10 +4663,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4680,13 +4689,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4737,7 +4746,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4754,10 +4763,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4780,13 +4789,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4837,7 +4846,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
